--- a/benchmark/data/bench_tables.xlsx
+++ b/benchmark/data/bench_tables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\merag\Git\BioRedis_engine\benchmark\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86ECFF7-B119-4A2D-80AB-6875EA2AAF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5797245-C6B0-4857-B1EA-3F3F2919B6BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="69">
   <si>
     <t>VectorBuilder</t>
   </si>
@@ -230,7 +230,10 @@
     <t>https://bioredis.cs.put.poznan.pl/frontend</t>
   </si>
   <si>
-    <t>BioRedis</t>
+    <t>BIOREDIS</t>
+  </si>
+  <si>
+    <t>Addgene</t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1235,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="H2" t="s">
         <v>27</v>
@@ -1278,7 +1281,7 @@
         <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
         <v>31</v>
